--- a/SGC-CKN/Excel/72390059-8571-418d-8dc3-aac09a9c2ceb_CT-02_P7-84_D800_07-03-2026.xlsx
+++ b/SGC-CKN/Excel/72390059-8571-418d-8dc3-aac09a9c2ceb_CT-02_P7-84_D800_07-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -115,17 +115,21 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">08:15
+    <t xml:space="preserve">07:16
 07/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">08:16
+07/03/2026</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">09:45
+    <t xml:space="preserve">09:46
 07/03/2026</t>
   </si>
   <si>
@@ -355,7 +359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -365,12 +369,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -536,17 +540,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,16 +1210,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.65</v>
+        <v>-1.1</v>
       </c>
       <c r="H11" s="5">
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="J11" s="8">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1232,13 +1236,13 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.65</v>
+        <v>-1.1</v>
       </c>
       <c r="G12" s="9">
         <v>-7.6</v>
@@ -1247,80 +1251,80 @@
         <v>1</v>
       </c>
       <c r="I12" s="9">
-        <v>5.95</v>
-      </c>
-      <c r="J12" s="8">
-        <v>5.95</v>
+        <v>6.5</v>
+      </c>
+      <c r="J12" s="12">
+        <v>6.5</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="E13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="13">
         <v>-7.6</v>
       </c>
-      <c r="G13" s="12">
-        <v>-12.6</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="13">
+        <v>-9.6</v>
+      </c>
+      <c r="H13" s="13">
         <v>1.5</v>
       </c>
-      <c r="I13" s="12">
-        <v>5</v>
-      </c>
-      <c r="J13" s="15">
-        <v>3.33</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="I13" s="13">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.33</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
-        <v>-12.6</v>
+        <v>-9.6</v>
       </c>
       <c r="G14" s="16">
         <v>-17.8</v>
       </c>
       <c r="H14" s="16">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I14" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="J14" s="8">
-        <v>20.8</v>
+        <v>8.2</v>
+      </c>
+      <c r="J14" s="12">
+        <v>35.14</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1328,19 +1332,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-17.8</v>
@@ -1354,7 +1358,7 @@
       <c r="I15" s="19">
         <v>4.3</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="12">
         <v>5.73</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1363,19 +1367,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-22.1</v>
@@ -1389,7 +1393,7 @@
       <c r="I16" s="22">
         <v>4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="12">
         <v>16</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1398,19 +1402,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-26.1</v>
@@ -1424,7 +1428,7 @@
       <c r="I17" s="25">
         <v>10</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="12">
         <v>120</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1433,19 +1437,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-36.1</v>
@@ -1459,7 +1463,7 @@
       <c r="I18" s="28">
         <v>1.5</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="8">
         <v>3.6</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1468,34 +1472,34 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="31">
         <v>-37.6</v>
       </c>
       <c r="G19" s="31">
-        <v>-43.1</v>
+        <v>-40.1</v>
       </c>
       <c r="H19" s="31">
         <v>0.42</v>
       </c>
       <c r="I19" s="31">
-        <v>5.5</v>
-      </c>
-      <c r="J19" s="8">
-        <v>13.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="12">
+        <v>6</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1503,22 +1507,22 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" s="34">
-        <v>-43.1</v>
+        <v>-40.1</v>
       </c>
       <c r="G20" s="34">
         <v>-45.05</v>
@@ -1527,10 +1531,10 @@
         <v>0.08</v>
       </c>
       <c r="I20" s="34">
-        <v>1.95</v>
-      </c>
-      <c r="J20" s="8">
-        <v>23.4</v>
+        <v>4.95</v>
+      </c>
+      <c r="J20" s="12">
+        <v>59.4</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1538,7 +1542,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1644,31 +1648,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1688,16 +1692,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.65</v>
+        <v>-1.1</v>
       </c>
       <c r="G2" s="5">
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="I2" s="8">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.65</v>
+        <v>-1.1</v>
       </c>
       <c r="F3" s="9">
         <v>-7.6</v>
@@ -1723,39 +1727,39 @@
         <v>1</v>
       </c>
       <c r="H3" s="9">
-        <v>5.95</v>
-      </c>
-      <c r="I3" s="8">
-        <v>5.95</v>
+        <v>6.5</v>
+      </c>
+      <c r="I3" s="12">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-7.6</v>
       </c>
-      <c r="F4" s="12">
-        <v>-12.6</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13">
+        <v>-9.6</v>
+      </c>
+      <c r="G4" s="13">
         <v>1.5</v>
       </c>
-      <c r="H4" s="12">
-        <v>5</v>
-      </c>
-      <c r="I4" s="15">
-        <v>3.33</v>
+      <c r="H4" s="13">
+        <v>2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1.33</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1766,25 +1770,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-12.6</v>
+        <v>-9.6</v>
       </c>
       <c r="F5" s="16">
         <v>-17.8</v>
       </c>
       <c r="G5" s="16">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H5" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="I5" s="8">
-        <v>20.8</v>
+        <v>8.2</v>
+      </c>
+      <c r="I5" s="12">
+        <v>35.14</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,7 +1799,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1812,7 +1816,7 @@
       <c r="H6" s="19">
         <v>4.3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="12">
         <v>5.73</v>
       </c>
     </row>
@@ -1824,7 +1828,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1841,7 +1845,7 @@
       <c r="H7" s="22">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="12">
         <v>16</v>
       </c>
     </row>
@@ -1853,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1870,7 +1874,7 @@
       <c r="H8" s="25">
         <v>10</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="12">
         <v>120</v>
       </c>
     </row>
@@ -1882,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1899,7 +1903,7 @@
       <c r="H9" s="28">
         <v>1.5</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="8">
         <v>3.6</v>
       </c>
     </row>
@@ -1911,7 +1915,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1920,16 +1924,16 @@
         <v>-37.6</v>
       </c>
       <c r="F10" s="31">
-        <v>-43.1</v>
+        <v>-40.1</v>
       </c>
       <c r="G10" s="31">
         <v>0.42</v>
       </c>
       <c r="H10" s="31">
-        <v>5.5</v>
-      </c>
-      <c r="I10" s="8">
-        <v>13.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="I10" s="12">
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1940,13 +1944,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-43.1</v>
+        <v>-40.1</v>
       </c>
       <c r="F11" s="34">
         <v>-45.05</v>
@@ -1955,15 +1959,15 @@
         <v>0.08</v>
       </c>
       <c r="H11" s="34">
-        <v>1.95</v>
-      </c>
-      <c r="I11" s="8">
-        <v>23.4</v>
+        <v>4.95</v>
+      </c>
+      <c r="I11" s="12">
+        <v>59.4</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1981,13 +1985,13 @@
         <v>-45.05</v>
       </c>
       <c r="G12" s="39">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="H12" s="39">
         <v>45.05</v>
       </c>
       <c r="I12" s="39">
-        <v>9.01</v>
+        <v>9.04</v>
       </c>
     </row>
   </sheetData>
